--- a/CS1/chapter8-HPU/Unplugged_Activities/MoreProcessors(MP)/timing_sheet.xlsx
+++ b/CS1/chapter8-HPU/Unplugged_Activities/MoreProcessors(MP)/timing_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HPU 2026\EduPar Documents\MP Activity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE7B037-9168-4D5D-B2F8-8FCC6148256A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{707C5F3B-43CB-4A7B-9BC1-225618874806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,16 +52,16 @@
     <t>Total Time</t>
   </si>
   <si>
-    <t>45–65</t>
-  </si>
-  <si>
     <t>Pre-survey (optional)</t>
   </si>
   <si>
     <t>Post-survey/Engagement Survey (optional)</t>
   </si>
   <si>
-    <t>Estimated Time for the MPWritingActivity</t>
+    <t>39-60</t>
+  </si>
+  <si>
+    <t>Estimated Time for the MP Writing Activity</t>
   </si>
 </sst>
 </file>
@@ -438,7 +438,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -478,7 +478,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>2</v>
@@ -489,7 +489,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
